--- a/site/leagues/proliga/2026_2027/xlsx/context_packs/context_pack_SBC.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/context_packs/context_pack_SBC.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.8</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>79.8</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-5.0</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q4 (2.5)</t>
+          <t>Q4 (2.7)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q1 (-2)</t>
+          <t>Q3 (-2.7)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 5 | fora: -8</t>
+          <t>Diff médio casa: 5 | fora: -5</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff médio em vitórias: 5 | em derrotas: -8</t>
+          <t>Diff médio em vitórias: 5 | em derrotas: -5</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melhor período: Q4 (2.5)</t>
+          <t>Melhor período: Q4 (2.7)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pior período: Q1 (-2)</t>
+          <t>Pior período: Q3 (-2.7)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Tavares sobe mais em vitórias (11 ppg).</t>
+          <t>M. Tavares sobe mais em vitórias (12 ppg).</t>
         </is>
       </c>
     </row>
@@ -843,25 +843,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="F2" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="G2" t="n">
-        <v>82</v>
+        <v>74.5</v>
       </c>
       <c r="H2" t="n">
-        <v>90</v>
+        <v>79.5</v>
       </c>
       <c r="I2" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="3">
@@ -1010,13 +1010,13 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>39.2</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>-7</v>
+        <v>-4.5</v>
       </c>
       <c r="H2" t="n">
         <v>19</v>
@@ -1025,16 +1025,16 @@
         <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>-7</v>
+        <v>-4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1053,13 +1053,13 @@
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>25.1</v>
+        <v>24.4</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>-2</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="n">
         <v>12</v>
@@ -1068,16 +1068,16 @@
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>-2</v>
+        <v>1.5</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1096,13 +1096,13 @@
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>11.7</v>
+        <v>15.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>-12</v>
+        <v>-7.5</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -1111,16 +1111,16 @@
         <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>-12</v>
+        <v>-7.5</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1139,13 +1139,13 @@
         <v>-3</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>17.6</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1169,87 +1169,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. Hall</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.9</v>
+        <v>36.4</v>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>32.9</v>
+        <v>35.5</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>27.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>27.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>D. Hall</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36.4</v>
+        <v>30.9</v>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>34.8</v>
+        <v>36.5</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L7" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="M7" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
@@ -1268,13 +1268,13 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1283,16 +1283,16 @@
         <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="K8" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="L8" t="n">
-        <v>-11</v>
+        <v>-5.5</v>
       </c>
       <c r="M8" t="n">
-        <v>-11</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="9">
@@ -1431,25 +1431,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H2" t="n">
         <v>-4</v>
       </c>
       <c r="I2" t="n">
-        <v>20.5</v>
+        <v>18.7</v>
       </c>
       <c r="J2" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>-2</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="3">
@@ -1474,25 +1474,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H3" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="I3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="J3" t="n">
-        <v>20.5</v>
+        <v>18.7</v>
       </c>
       <c r="K3" t="n">
-        <v>-2</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="4">
@@ -1517,25 +1517,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="I4" t="n">
-        <v>21.5</v>
+        <v>19.7</v>
       </c>
       <c r="J4" t="n">
-        <v>21.5</v>
+        <v>22.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="5">
@@ -1560,25 +1560,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>23</v>
+        <v>21.3</v>
       </c>
       <c r="J5" t="n">
-        <v>20.5</v>
+        <v>18.7</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -1599,20 +1599,20 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1709,52 +1709,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -1764,52 +1764,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>9.5</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -1819,52 +1819,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="H4" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -2039,23 +2039,23 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -2063,10 +2063,10 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -2102,7 +2102,7 @@
         <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0.5</v>
@@ -2138,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2245,8 +2245,37 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2923000</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>67</v>
+      </c>
+      <c r="F4" t="n">
+        <v>69</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>